--- a/Quality Data.xlsx
+++ b/Quality Data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>#</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>PURE GOLD</t>
+  </si>
+  <si>
+    <t>SUNSHINE</t>
   </si>
 </sst>
 </file>
@@ -434,6 +437,12 @@
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Quality Data.xlsx
+++ b/Quality Data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>#</t>
   </si>
@@ -40,6 +40,9 @@
   </si>
   <si>
     <t>SUNSHINE</t>
+  </si>
+  <si>
+    <t>VAARI CHIFFON</t>
   </si>
 </sst>
 </file>
@@ -371,10 +374,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -442,6 +445,17 @@
       </c>
       <c r="C6">
         <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
